--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7402,7 +7402,7 @@
         <v>13447</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -10987,7 +10987,7 @@
         <v>4516</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -14572,7 +14572,7 @@
         <v>5150</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -23921,7 +23921,7 @@
         <v>17100</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -30401,7 +30401,7 @@
         <v>11605</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -43886,7 +43886,7 @@
         <v>5639</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7402,7 +7402,7 @@
         <v>13447</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -14572,7 +14572,7 @@
         <v>5150</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -23921,7 +23921,7 @@
         <v>17100</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -30401,7 +30401,7 @@
         <v>11605</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -40301,7 +40301,7 @@
         <v>1850</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -7399,10 +7399,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J64" t="n">
-        <v>13447</v>
+        <v>13465</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -10969,7 +10969,7 @@
         <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -14554,7 +14554,7 @@
         <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -14569,10 +14569,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J64" t="n">
-        <v>5150</v>
+        <v>5156</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -23918,10 +23918,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J64" t="n">
-        <v>17100</v>
+        <v>17126</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -30398,10 +30398,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J64" t="n">
-        <v>11605</v>
+        <v>11625</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43868,7 +43868,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -43883,10 +43883,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J64" t="n">
-        <v>5639</v>
+        <v>5644</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -10969,7 +10969,7 @@
         <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -10984,10 +10984,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J64" t="n">
-        <v>4516</v>
+        <v>4518</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -14554,7 +14554,7 @@
         <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -23918,7 +23918,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J64" t="n">
-        <v>17126</v>
+        <v>17133</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -40298,10 +40298,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -43868,7 +43868,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -43883,10 +43883,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J64" t="n">
-        <v>5644</v>
+        <v>5645</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -10969,7 +10969,7 @@
         <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -14554,7 +14554,7 @@
         <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43868,7 +43868,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -10969,7 +10969,7 @@
         <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -14554,7 +14554,7 @@
         <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43868,7 +43868,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7399,7 +7399,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J64" t="n">
-        <v>13465</v>
+        <v>13464</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -23918,7 +23918,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J64" t="n">
-        <v>17133</v>
+        <v>17134</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7769,7 +7769,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13463</v>
+        <v>13462</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7772,7 +7772,7 @@
         <v>13462</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13462</v>
+        <v>13473</v>
       </c>
       <c r="K73" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11394,7 +11394,7 @@
         <v>4518</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -24476,7 +24476,7 @@
         <v>17134</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -31027,7 +31027,7 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11625</v>
+        <v>11619</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -7772,7 +7772,7 @@
         <v>13473</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -11394,7 +11394,7 @@
         <v>4518</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24473,10 +24473,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17134</v>
+        <v>17142</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31027,7 +31027,7 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11619</v>
+        <v>11616</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11616</v>
+        <v>11615</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -36757,7 +36757,7 @@
         <v>142</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -44700,7 +44700,7 @@
         <v>5645</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31030,7 +31030,7 @@
         <v>11615</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -44700,7 +44700,7 @@
         <v>5645</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -31030,7 +31030,7 @@
         <v>11615</v>
       </c>
       <c r="K73" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -38196,7 +38196,7 @@
         <v>639</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7772,7 +7772,7 @@
         <v>13473</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -24476,7 +24476,7 @@
         <v>17142</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -31030,7 +31030,7 @@
         <v>11615</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -44700,7 +44700,7 @@
         <v>5645</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13473</v>
+        <v>13476</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11391,10 +11391,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J73" t="n">
-        <v>4518</v>
+        <v>4522</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -15016,7 +15016,7 @@
         <v>5156</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -24473,10 +24473,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17142</v>
+        <v>17153</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11615</v>
+        <v>11631</v>
       </c>
       <c r="K73" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -44697,10 +44697,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J73" t="n">
-        <v>5645</v>
+        <v>5650</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13476</v>
+        <v>13475</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -15013,7 +15013,7 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J73" t="n">
-        <v>5156</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
@@ -31030,7 +31030,7 @@
         <v>11631</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -44700,7 +44700,7 @@
         <v>5650</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -7769,7 +7769,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13475</v>
+        <v>13474</v>
       </c>
       <c r="K73" t="n">
         <v>2</v>
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -15013,10 +15013,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>5157</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24476,7 +24476,7 @@
         <v>17153</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31030,7 +31030,7 @@
         <v>11631</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13474</v>
+        <v>13479</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -15013,7 +15013,7 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J73" t="n">
-        <v>5157</v>
+        <v>5165</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -18043,10 +18043,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -24473,10 +24473,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17153</v>
+        <v>17165</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11631</v>
+        <v>11637</v>
       </c>
       <c r="K73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -36754,10 +36754,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -38193,10 +38193,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -44700,7 +44700,7 @@
         <v>5650</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7772,7 +7772,7 @@
         <v>13479</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -11394,7 +11394,7 @@
         <v>4522</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -15016,7 +15016,7 @@
         <v>5165</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -24476,7 +24476,7 @@
         <v>17165</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11637</v>
+        <v>11642</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -41078,7 +41078,7 @@
         <v>1851</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -44700,7 +44700,7 @@
         <v>5650</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -11394,7 +11394,7 @@
         <v>4522</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -24476,7 +24476,7 @@
         <v>17165</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -31030,7 +31030,7 @@
         <v>11642</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13479</v>
+        <v>13478</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -11391,10 +11391,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J73" t="n">
-        <v>4522</v>
+        <v>4529</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -15016,7 +15016,7 @@
         <v>5165</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24473,10 +24473,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17165</v>
+        <v>17193</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11642</v>
+        <v>11671</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -41078,7 +41078,7 @@
         <v>1851</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -44697,10 +44697,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J73" t="n">
-        <v>5650</v>
+        <v>5655</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13478</v>
+        <v>13487</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -11394,7 +11394,7 @@
         <v>4529</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -15016,7 +15016,7 @@
         <v>5165</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24476,7 +24476,7 @@
         <v>17193</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11671</v>
+        <v>11670</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -41075,10 +41075,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1851</v>
+        <v>1904</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -44700,7 +44700,7 @@
         <v>5655</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13487</v>
+        <v>13494</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -11394,7 +11394,7 @@
         <v>4529</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -15013,10 +15013,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J73" t="n">
-        <v>5165</v>
+        <v>5172</v>
       </c>
       <c r="K73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24473,10 +24473,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17193</v>
+        <v>17211</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11670</v>
+        <v>11675</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -44697,10 +44697,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J73" t="n">
-        <v>5655</v>
+        <v>5660</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -7772,7 +7772,7 @@
         <v>13494</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -11376,7 +11376,7 @@
         <v>0.003779808947838637</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -15016,7 +15016,7 @@
         <v>5172</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.04491347144427803</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24473,7 +24473,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17211</v>
+        <v>17223</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.002380786546023263</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11675</v>
+        <v>11679</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -44700,7 +44700,7 @@
         <v>5660</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7769,10 +7769,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13494</v>
+        <v>13506</v>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -11391,10 +11391,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J73" t="n">
-        <v>4529</v>
+        <v>4533</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -15013,10 +15013,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J73" t="n">
-        <v>5172</v>
+        <v>5175</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -24473,7 +24473,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17223</v>
+        <v>17229</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -31027,10 +31027,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J73" t="n">
-        <v>11679</v>
+        <v>11681</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -44697,10 +44697,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J73" t="n">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7769,7 +7769,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J73" t="n">
-        <v>13506</v>
+        <v>13505</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -11367,13 +11367,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>87636</v>
+        <v>87758</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.003779808947838637</v>
+        <v>0.005177192861888072</v>
       </c>
       <c r="E73" t="n">
         <v>9</v>
@@ -11410,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.08834269021863161</v>
+        <v>-0.08961006403974567</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -18043,10 +18043,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -24449,13 +24449,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>241398</v>
+        <v>233142</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.04491347144427803</v>
+        <v>0.00917661521413545</v>
       </c>
       <c r="E73" t="n">
         <v>9</v>
@@ -24492,7 +24492,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.789173895392671</v>
+        <v>0.8525319333281862</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -31003,13 +31003,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>158307</v>
+        <v>158699</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.002380786546023263</v>
+        <v>0.004862883157834751</v>
       </c>
       <c r="E73" t="n">
         <v>9</v>
@@ -31046,7 +31046,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.2062006102067502</v>
+        <v>-0.2081613620753754</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -11376,7 +11376,7 @@
         <v>0.005177192861888072</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -14998,7 +14998,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -24458,7 +24458,7 @@
         <v>0.00917661521413545</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24473,7 +24473,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J73" t="n">
-        <v>17229</v>
+        <v>17228</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -27501,7 +27501,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -31012,7 +31012,7 @@
         <v>0.004862883157834751</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -38178,7 +38178,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -41060,7 +41060,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -44682,7 +44682,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -47712,7 +47712,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -1416,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4132,7 +4132,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4452,20 +4452,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5533</v>
+        <v>5967</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.05547968589962445</v>
+        <v>0.01860703311710481</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -4480,16 +4480,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>303</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4499,10 +4499,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.07273336685101391</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -4517,10 +4517,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -4563,7 +4563,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -4591,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4631,26 +4631,26 @@
         <v>265</v>
       </c>
       <c r="K86" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5592</v>
+        <v>5533</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01066329296945599</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4665,16 +4665,16 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4684,10 +4684,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.01066329296945599</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4711,20 +4711,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>5858</v>
+        <v>5592</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.04756795422031473</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4748,20 +4748,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5533</v>
+        <v>5858</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.05547968589962445</v>
+        <v>0.04756795422031473</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -4776,16 +4776,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>293</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4795,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.05547968589962445</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -4813,16 +4813,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -4850,16 +4850,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -4890,26 +4890,26 @@
         <v>265</v>
       </c>
       <c r="K93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>5592</v>
+        <v>5533</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01066329296945599</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -4924,105 +4924,142 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5609</v>
+        <v>5592</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.003040057224606581</v>
+        <v>0.01066329296945599</v>
       </c>
       <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>276</v>
+      </c>
+      <c r="K95" t="n">
         <v>1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>283</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5609</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.003040057224606581</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>283</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>5858</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.04439293991798895</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>7</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>294</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>325</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>83</v>
       </c>
     </row>
@@ -5038,7 +5075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7754,7 +7791,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>103148</v>
@@ -8074,60 +8111,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>192094</v>
+        <v>203367</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.05425990202594589</v>
+        <v>0.001240676464072077</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>17867</v>
+        <v>103148</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>5984</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.8332244334092521</v>
+        <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>10485</v>
+        <v>13504</v>
       </c>
       <c r="K82" t="n">
-        <v>893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>194152</v>
+        <v>192094</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.01071350484658553</v>
+        <v>-0.05543180555350671</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>77599</v>
+        <v>17867</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -8136,13 +8173,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>3.343146583086137</v>
+        <v>-0.8362808342191108</v>
       </c>
       <c r="J83" t="n">
-        <v>11468</v>
+        <v>10485</v>
       </c>
       <c r="K83" t="n">
-        <v>90</v>
+        <v>893</v>
       </c>
     </row>
     <row r="84">
@@ -8158,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.01071350484658553</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -8173,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>3.343146583086137</v>
       </c>
       <c r="J84" t="n">
         <v>11468</v>
@@ -8185,23 +8222,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>195889</v>
+        <v>194152</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.008946598541349046</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>84997</v>
+        <v>77599</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -8210,35 +8247,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.09533628010670241</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>11352</v>
+        <v>11468</v>
       </c>
       <c r="K85" t="n">
-        <v>185</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>196406</v>
+        <v>195889</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.002639249779211696</v>
+        <v>0.008946598541349046</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
-        <v>86392</v>
+        <v>84997</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -8247,32 +8284,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.01641234396508112</v>
+        <v>0.09533628010670241</v>
       </c>
       <c r="J86" t="n">
-        <v>11285</v>
+        <v>11352</v>
       </c>
       <c r="K86" t="n">
-        <v>459</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>198181</v>
+        <v>196406</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.009037402116024969</v>
+        <v>0.002639249779211696</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>86392</v>
@@ -8284,35 +8321,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>0.01641234396508112</v>
       </c>
       <c r="J87" t="n">
-        <v>12138</v>
+        <v>11285</v>
       </c>
       <c r="K87" t="n">
-        <v>57</v>
+        <v>459</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>203106</v>
+        <v>198181</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.0248510200271469</v>
+        <v>0.009037402116024969</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>97462</v>
+        <v>86392</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -8321,47 +8358,47 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.128136864524493</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>12692</v>
+        <v>12138</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>203115</v>
+        <v>203106</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>4.431183716876902e-05</v>
+        <v>0.0248510200271469</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>104147</v>
+        <v>97462</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2985</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.09921815682009398</v>
+        <v>0.128136864524493</v>
       </c>
       <c r="J89" t="n">
-        <v>13141</v>
+        <v>12692</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -8370,60 +8407,60 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>192094</v>
+        <v>203115</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.05425990202594589</v>
+        <v>4.431183716876902e-05</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>17867</v>
+        <v>104147</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>2985</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.8332244334092521</v>
+        <v>0.09921815682009398</v>
       </c>
       <c r="J90" t="n">
-        <v>10485</v>
+        <v>13141</v>
       </c>
       <c r="K90" t="n">
-        <v>893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>194152</v>
+        <v>192094</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01071350484658553</v>
+        <v>-0.05425990202594589</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>77599</v>
+        <v>17867</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -8432,35 +8469,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>3.343146583086137</v>
+        <v>-0.8332244334092521</v>
       </c>
       <c r="J91" t="n">
-        <v>11465</v>
+        <v>10485</v>
       </c>
       <c r="K91" t="n">
-        <v>120</v>
+        <v>893</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>195908</v>
+        <v>194152</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.009044460010713256</v>
+        <v>0.01071350484658553</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
-        <v>84997</v>
+        <v>77599</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -8469,35 +8506,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.09533628010670241</v>
+        <v>3.343146583086137</v>
       </c>
       <c r="J92" t="n">
-        <v>11348</v>
+        <v>11465</v>
       </c>
       <c r="K92" t="n">
-        <v>218</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>196741</v>
+        <v>195908</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.004251995834779591</v>
+        <v>0.009044460010713256</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
-        <v>86392</v>
+        <v>84997</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -8506,32 +8543,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01641234396508112</v>
+        <v>0.09533628010670241</v>
       </c>
       <c r="J93" t="n">
-        <v>11283</v>
+        <v>11348</v>
       </c>
       <c r="K93" t="n">
-        <v>459</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>198544</v>
+        <v>196741</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.009164332803025298</v>
+        <v>0.004251995834779591</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>86392</v>
@@ -8543,35 +8580,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.01641234396508112</v>
       </c>
       <c r="J94" t="n">
-        <v>12188</v>
+        <v>11283</v>
       </c>
       <c r="K94" t="n">
-        <v>54</v>
+        <v>459</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>203233</v>
+        <v>198544</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.02361693125956967</v>
+        <v>0.009164332803025298</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>101940</v>
+        <v>86392</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -8580,71 +8617,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.1799703676266321</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>12725</v>
+        <v>12188</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>203233</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.02361693125956967</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>101940</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.1799703676266321</v>
+      </c>
+      <c r="J96" t="n">
+        <v>12725</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>203115</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>-0.0005806143687294878</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>7</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>103148</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>3921</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.0503139101432215</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>13184</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>11021</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>85281</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>3921</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>2699</v>
       </c>
     </row>
@@ -8660,7 +8734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11376,7 +11450,7 @@
         <v>0.005177192861888072</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>41946</v>
@@ -11696,23 +11770,23 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>79898</v>
+        <v>87758</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.08485098389572308</v>
+        <v>0.005177192861888072</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>8616</v>
+        <v>41946</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -11721,35 +11795,35 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.5402347918890075</v>
+        <v>1.238313767342583</v>
       </c>
       <c r="J82" t="n">
-        <v>3494</v>
+        <v>4533</v>
       </c>
       <c r="K82" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>80678</v>
+        <v>79898</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.009762447120078099</v>
+        <v>-0.0895644841495932</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>18740</v>
+        <v>8616</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -11758,13 +11832,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>1.175023212627669</v>
+        <v>-0.7945930482048348</v>
       </c>
       <c r="J83" t="n">
-        <v>3463</v>
+        <v>3494</v>
       </c>
       <c r="K83" t="n">
-        <v>660</v>
+        <v>528</v>
       </c>
     </row>
     <row r="84">
@@ -11780,7 +11854,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.009762447120078099</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -11795,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>1.175023212627669</v>
       </c>
       <c r="J84" t="n">
         <v>3463</v>
@@ -11807,20 +11881,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>81695</v>
+        <v>80678</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.01260566697240884</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>18740</v>
@@ -11835,29 +11909,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>3912</v>
+        <v>3463</v>
       </c>
       <c r="K85" t="n">
-        <v>34</v>
+        <v>660</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>81707</v>
+        <v>81695</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.0001468878144317278</v>
+        <v>0.01260566697240884</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>18740</v>
@@ -11872,29 +11946,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>3909</v>
+        <v>3912</v>
       </c>
       <c r="K86" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>83082</v>
+        <v>81707</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01682842351328527</v>
+        <v>0.0001468878144317278</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>18740</v>
@@ -11909,29 +11983,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>4140</v>
+        <v>3909</v>
       </c>
       <c r="K87" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>84237</v>
+        <v>83082</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.01390192821549794</v>
+        <v>0.01682842351328527</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>18740</v>
@@ -11946,29 +12020,29 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>4301</v>
+        <v>4140</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>87336</v>
+        <v>84237</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.03678905943943873</v>
+        <v>0.01390192821549794</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
         <v>18740</v>
@@ -11983,7 +12057,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>4447</v>
+        <v>4301</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -11992,23 +12066,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>79898</v>
+        <v>87336</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.0851653384629477</v>
+        <v>0.03678905943943873</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>8616</v>
+        <v>18740</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -12017,35 +12091,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.5402347918890075</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>3494</v>
+        <v>4447</v>
       </c>
       <c r="K90" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>80678</v>
+        <v>79898</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.009762447120078099</v>
+        <v>-0.0851653384629477</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>18740</v>
+        <v>8616</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -12054,32 +12128,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>1.175023212627669</v>
+        <v>-0.5402347918890075</v>
       </c>
       <c r="J91" t="n">
-        <v>3463</v>
+        <v>3494</v>
       </c>
       <c r="K91" t="n">
-        <v>664</v>
+        <v>528</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>81695</v>
+        <v>80678</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.01260566697240884</v>
+        <v>0.009762447120078099</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>18740</v>
@@ -12091,32 +12165,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.175023212627669</v>
       </c>
       <c r="J92" t="n">
-        <v>3911</v>
+        <v>3463</v>
       </c>
       <c r="K92" t="n">
-        <v>41</v>
+        <v>664</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>81707</v>
+        <v>81695</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.0001468878144317278</v>
+        <v>0.01260566697240884</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>18740</v>
@@ -12131,29 +12205,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>3909</v>
+        <v>3911</v>
       </c>
       <c r="K93" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>83088</v>
+        <v>81707</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01690185663407052</v>
+        <v>0.0001468878144317278</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>18740</v>
@@ -12168,29 +12242,29 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>4140</v>
+        <v>3909</v>
       </c>
       <c r="K94" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>85106</v>
+        <v>83088</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.02428750240708646</v>
+        <v>0.01690185663407052</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
         <v>18740</v>
@@ -12205,29 +12279,29 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>4314</v>
+        <v>4140</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>87336</v>
+        <v>85106</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.0262026179117806</v>
+        <v>0.02428750240708646</v>
       </c>
       <c r="E96" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>18740</v>
@@ -12242,31 +12316,68 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
+        <v>4314</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>87336</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.0262026179117806</v>
+      </c>
+      <c r="E97" t="n">
+        <v>7</v>
+      </c>
+      <c r="F97" t="n">
+        <v>18740</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>4462</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>7438</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>10124</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>968</v>
       </c>
     </row>
@@ -12282,7 +12393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14998,7 +15109,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>66160</v>
@@ -15318,60 +15429,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>80906</v>
+        <v>91684</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1121718900886665</v>
+        <v>0.006101308050215082</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>51567</v>
+        <v>66160</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.2235522630770621</v>
+        <v>0.0008733098443099346</v>
       </c>
       <c r="J82" t="n">
-        <v>3111</v>
+        <v>5175</v>
       </c>
       <c r="K82" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>85386</v>
+        <v>80906</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.05537290188613947</v>
+        <v>-0.1175559530561494</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>66160</v>
+        <v>51567</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -15380,13 +15491,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.2829910601741424</v>
+        <v>-0.2242297508725478</v>
       </c>
       <c r="J83" t="n">
-        <v>3085</v>
+        <v>3111</v>
       </c>
       <c r="K83" t="n">
-        <v>1284</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="84">
@@ -15402,7 +15513,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.05537290188613947</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -15417,7 +15528,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.2829910601741424</v>
       </c>
       <c r="J84" t="n">
         <v>3085</v>
@@ -15429,20 +15540,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>87037</v>
+        <v>85386</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.01933572248377954</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>66160</v>
@@ -15457,29 +15568,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>4385</v>
+        <v>3085</v>
       </c>
       <c r="K85" t="n">
-        <v>75</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>86999</v>
+        <v>87037</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.0004365959304663534</v>
+        <v>0.01933572248377954</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>66160</v>
@@ -15494,29 +15605,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>4379</v>
+        <v>4385</v>
       </c>
       <c r="K86" t="n">
-        <v>141</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>87774</v>
+        <v>86999</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.008908148369521489</v>
+        <v>-0.0004365959304663534</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>66160</v>
@@ -15531,29 +15642,29 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>4695</v>
+        <v>4379</v>
       </c>
       <c r="K87" t="n">
-        <v>29</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>90188</v>
+        <v>87774</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.02750244947250894</v>
+        <v>0.008908148369521489</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>66160</v>
@@ -15568,32 +15679,32 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>4887</v>
+        <v>4695</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>91566</v>
+        <v>90188</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01527919457133987</v>
+        <v>0.02750244947250894</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>66414</v>
+        <v>66160</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -15602,10 +15713,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.003839177750906892</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>5032</v>
+        <v>4887</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -15614,23 +15725,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>80906</v>
+        <v>91566</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1164187580542996</v>
+        <v>0.01527919457133987</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>51567</v>
+        <v>66414</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -15639,35 +15750,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.2235522630770621</v>
+        <v>0.003839177750906892</v>
       </c>
       <c r="J90" t="n">
-        <v>3111</v>
+        <v>5032</v>
       </c>
       <c r="K90" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>86199</v>
+        <v>80906</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.0654216003757447</v>
+        <v>-0.1164187580542996</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>66160</v>
+        <v>51567</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -15676,32 +15787,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.2829910601741424</v>
+        <v>-0.2235522630770621</v>
       </c>
       <c r="J91" t="n">
-        <v>3085</v>
+        <v>3111</v>
       </c>
       <c r="K91" t="n">
-        <v>1290</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>87037</v>
+        <v>86199</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.009721690506850428</v>
+        <v>0.0654216003757447</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>66160</v>
@@ -15713,32 +15824,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.2829910601741424</v>
       </c>
       <c r="J92" t="n">
-        <v>4385</v>
+        <v>3085</v>
       </c>
       <c r="K92" t="n">
-        <v>85</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>86999</v>
+        <v>87037</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.0004365959304663534</v>
+        <v>0.009721690506850428</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>66160</v>
@@ -15753,29 +15864,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>4378</v>
+        <v>4385</v>
       </c>
       <c r="K93" t="n">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>87774</v>
+        <v>86999</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.008908148369521489</v>
+        <v>-0.0004365959304663534</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>66160</v>
@@ -15790,32 +15901,32 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>4695</v>
+        <v>4378</v>
       </c>
       <c r="K94" t="n">
-        <v>36</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>90331</v>
+        <v>87774</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.02913163351334108</v>
+        <v>0.008908148369521489</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>66414</v>
+        <v>66160</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -15824,71 +15935,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.003839177750906892</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>4903</v>
+        <v>4695</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>90331</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.02913163351334108</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>66414</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.003839177750906892</v>
+      </c>
+      <c r="J96" t="n">
+        <v>4903</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>91566</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.01367193986560539</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>7</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>66160</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>312</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.0008733098443099346</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>5037</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>10660</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>14593</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>312</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>1926</v>
       </c>
     </row>
@@ -15904,7 +16052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18028,7 +18176,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -18311,20 +18459,20 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>7484</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -18339,10 +18487,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>490</v>
+        <v>678</v>
       </c>
       <c r="K65" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -18358,7 +18506,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
@@ -18385,11 +18533,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>13340</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -18398,7 +18546,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -18416,13 +18564,13 @@
         <v>490</v>
       </c>
       <c r="K67" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -18435,7 +18583,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -18453,26 +18601,26 @@
         <v>490</v>
       </c>
       <c r="K68" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7484</v>
+        <v>13340</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.4389805097451274</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -18487,16 +18635,16 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>657</v>
+        <v>490</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -18506,10 +18654,10 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>-0.4389805097451274</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -18524,7 +18672,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -18533,7 +18681,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -18546,7 +18694,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -18561,7 +18709,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -18570,17 +18718,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>7484</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>5</v>
@@ -18598,29 +18746,29 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>490</v>
+        <v>674</v>
       </c>
       <c r="K72" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>13340</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18638,13 +18786,13 @@
         <v>490</v>
       </c>
       <c r="K73" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -18657,7 +18805,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -18675,26 +18823,26 @@
         <v>490</v>
       </c>
       <c r="K74" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7484</v>
+        <v>13340</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>-0.4389805097451274</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -18709,16 +18857,16 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>657</v>
+        <v>490</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -18728,10 +18876,10 @@
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0</v>
+        <v>-0.4389805097451274</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -18746,7 +18894,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -18755,7 +18903,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -18768,46 +18916,83 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>665</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7484</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
         <v>7</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
         <v>674</v>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B79" s="4" t="n">
         <v>-5602</v>
       </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>184</v>
       </c>
     </row>
@@ -18823,7 +19008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -20947,7 +21132,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -21230,7 +21415,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -21243,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -21258,7 +21443,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -21304,7 +21489,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -21317,7 +21502,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -21341,7 +21526,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -21354,7 +21539,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -21378,7 +21563,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -21391,7 +21576,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -21406,7 +21591,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -21415,7 +21600,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -21428,7 +21613,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -21452,7 +21637,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -21465,7 +21650,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -21489,7 +21674,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -21517,7 +21702,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -21526,7 +21711,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -21539,7 +21724,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -21563,7 +21748,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -21576,7 +21761,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -21600,7 +21785,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -21613,7 +21798,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -21628,7 +21813,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -21637,7 +21822,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -21650,7 +21835,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -21674,7 +21859,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -21687,7 +21872,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -21709,24 +21894,61 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21742,7 +21964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -24458,7 +24680,7 @@
         <v>0.00917661521413545</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>152356</v>
@@ -24778,60 +25000,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>184412</v>
+        <v>233142</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2087121813493068</v>
+        <v>0.0003818873818401823</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>27371</v>
+        <v>152356</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>4948</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>73479</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.8199122293354036</v>
+        <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>9274</v>
+        <v>17229</v>
       </c>
       <c r="K82" t="n">
-        <v>2818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>184103</v>
+        <v>184412</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.001675595948202937</v>
+        <v>-0.2090142488268952</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>86961</v>
+        <v>27371</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -24840,13 +25062,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>2.177121771217712</v>
+        <v>-0.8813994098352131</v>
       </c>
       <c r="J83" t="n">
-        <v>9191</v>
+        <v>9274</v>
       </c>
       <c r="K83" t="n">
-        <v>3446</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="84">
@@ -24862,7 +25084,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>-0.001675595948202937</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -24877,7 +25099,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>2.177121771217712</v>
       </c>
       <c r="J84" t="n">
         <v>9191</v>
@@ -24889,23 +25111,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>193713</v>
+        <v>184103</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.05219904075436033</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>95574</v>
+        <v>86961</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -24914,32 +25136,32 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.09904439921344051</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>11985</v>
+        <v>9191</v>
       </c>
       <c r="K85" t="n">
-        <v>1316</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>218168</v>
+        <v>193713</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.126243463267824</v>
+        <v>0.05219904075436033</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>95574</v>
@@ -24951,35 +25173,35 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.09904439921344051</v>
       </c>
       <c r="J86" t="n">
-        <v>12466</v>
+        <v>11985</v>
       </c>
       <c r="K86" t="n">
-        <v>1141</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>218403</v>
+        <v>218168</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.001077151552931686</v>
+        <v>0.126243463267824</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
-        <v>120136</v>
+        <v>95574</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -24988,35 +25210,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.2569945801159311</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>14210</v>
+        <v>12466</v>
       </c>
       <c r="K87" t="n">
-        <v>122</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>229476</v>
+        <v>218403</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.05069985302399693</v>
+        <v>0.001077151552931686</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>128117</v>
+        <v>120136</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -25025,35 +25247,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.06643304255177465</v>
+        <v>0.2569945801159311</v>
       </c>
       <c r="J88" t="n">
-        <v>15324</v>
+        <v>14210</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>233053</v>
+        <v>229476</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01558768672976695</v>
+        <v>0.05069985302399693</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>151987</v>
+        <v>128117</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -25062,35 +25284,35 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.1863140722932944</v>
+        <v>0.06643304255177465</v>
       </c>
       <c r="J89" t="n">
-        <v>16270</v>
+        <v>15324</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>184412</v>
+        <v>233053</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2087121813493068</v>
+        <v>0.01558768672976695</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>27371</v>
+        <v>151987</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -25099,35 +25321,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.8199122293354036</v>
+        <v>0.1863140722932944</v>
       </c>
       <c r="J90" t="n">
-        <v>9274</v>
+        <v>16270</v>
       </c>
       <c r="K90" t="n">
-        <v>2818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>184103</v>
+        <v>184412</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.001675595948202937</v>
+        <v>-0.2087121813493068</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>86961</v>
+        <v>27371</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -25136,35 +25358,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>2.177121771217712</v>
+        <v>-0.8199122293354036</v>
       </c>
       <c r="J91" t="n">
-        <v>9191</v>
+        <v>9274</v>
       </c>
       <c r="K91" t="n">
-        <v>3465</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>193896</v>
+        <v>184103</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.05319304954291891</v>
+        <v>-0.001675595948202937</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
-        <v>95574</v>
+        <v>86961</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -25173,32 +25395,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.09904439921344051</v>
+        <v>2.177121771217712</v>
       </c>
       <c r="J92" t="n">
-        <v>11985</v>
+        <v>9191</v>
       </c>
       <c r="K92" t="n">
-        <v>1340</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>218168</v>
+        <v>193896</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.1251805091389198</v>
+        <v>0.05319304954291891</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>95574</v>
@@ -25210,35 +25432,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.09904439921344051</v>
       </c>
       <c r="J93" t="n">
-        <v>12466</v>
+        <v>11985</v>
       </c>
       <c r="K93" t="n">
-        <v>1141</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>218427</v>
+        <v>218168</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.001187158520039603</v>
+        <v>0.1251805091389198</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>120136</v>
+        <v>95574</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -25247,35 +25469,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.2569945801159311</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>14351</v>
+        <v>12466</v>
       </c>
       <c r="K94" t="n">
-        <v>38</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>229476</v>
+        <v>218427</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.05058440577401146</v>
+        <v>0.001187158520039603</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>142208</v>
+        <v>120136</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -25284,71 +25506,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.1837251115402544</v>
+        <v>0.2569945801159311</v>
       </c>
       <c r="J95" t="n">
-        <v>15398</v>
+        <v>14351</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>229476</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.05058440577401146</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>142208</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.1837251115402544</v>
+      </c>
+      <c r="J96" t="n">
+        <v>15398</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>233053</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.01558768672976695</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>7</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>151988</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>30128</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.2806311881188119</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>16332</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>48641</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>124617</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>30128</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>7058</v>
       </c>
     </row>
@@ -25377,7 +25636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -27501,7 +27760,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -27784,20 +28043,20 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>12688</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -27812,10 +28071,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>121</v>
+        <v>203</v>
       </c>
       <c r="K65" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -27831,7 +28090,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
@@ -27858,11 +28117,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>12251</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -27871,7 +28130,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -27886,29 +28145,29 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>12841</v>
+        <v>12251</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.04815933393192393</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -27926,26 +28185,26 @@
         <v>183</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>12799</v>
+        <v>12841</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.003270773304259793</v>
+        <v>0.04815933393192393</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -27960,7 +28219,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
@@ -27969,20 +28228,20 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>12688</v>
+        <v>12799</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>-0.008672552543167435</v>
+        <v>-0.003270773304259793</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -27997,16 +28256,16 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -28016,10 +28275,10 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>-0.008672552543167435</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -28034,7 +28293,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -28043,17 +28302,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>12688</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>5</v>
@@ -28071,29 +28330,29 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>121</v>
+        <v>202</v>
       </c>
       <c r="K72" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>12251</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -28108,29 +28367,29 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>12841</v>
+        <v>12251</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.04815933393192393</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -28148,26 +28407,26 @@
         <v>183</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>12813</v>
+        <v>12841</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>-0.002180515536173195</v>
+        <v>0.04815933393192393</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -28182,7 +28441,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
@@ -28191,44 +28450,44 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>12688</v>
+        <v>12813</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>-0.009755716850074144</v>
+        <v>-0.002180515536173195</v>
       </c>
       <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>187</v>
+      </c>
+      <c r="K76" t="n">
         <v>1</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>193</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -28238,49 +28497,86 @@
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0</v>
+        <v>-0.009755716850074144</v>
       </c>
       <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>193</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>12688</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
         <v>7</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
         <v>202</v>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B79" s="4" t="n">
         <v>437</v>
       </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -28296,7 +28592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -31012,7 +31308,7 @@
         <v>0.004862883157834751</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>135985</v>
@@ -31332,60 +31628,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>125395</v>
+        <v>158699</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2041646569013226</v>
+        <v>0.007203422101495265</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>110011</v>
+        <v>135985</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.1927871739369703</v>
+        <v>0.0004769417030487581</v>
       </c>
       <c r="J82" t="n">
-        <v>7288</v>
+        <v>11681</v>
       </c>
       <c r="K82" t="n">
-        <v>1173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>132848</v>
+        <v>125395</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.05943618166593564</v>
+        <v>-0.2098563948103013</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>132992</v>
+        <v>110011</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -31394,13 +31690,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.2088972920889729</v>
+        <v>-0.1931719838650532</v>
       </c>
       <c r="J83" t="n">
-        <v>7267</v>
+        <v>7288</v>
       </c>
       <c r="K83" t="n">
-        <v>1772</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="84">
@@ -31416,7 +31712,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.05943618166593564</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -31431,7 +31727,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.2088972920889729</v>
       </c>
       <c r="J84" t="n">
         <v>7267</v>
@@ -31443,20 +31739,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>137128</v>
+        <v>132848</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.03221727086595207</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
         <v>132992</v>
@@ -31471,29 +31767,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>9097</v>
+        <v>7267</v>
       </c>
       <c r="K85" t="n">
-        <v>152</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>138931</v>
+        <v>137128</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.01314829939910157</v>
+        <v>0.03221727086595207</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>132992</v>
@@ -31508,29 +31804,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>9096</v>
+        <v>9097</v>
       </c>
       <c r="K86" t="n">
-        <v>407</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>146745</v>
+        <v>138931</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.05624374689594115</v>
+        <v>0.01314829939910157</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>132992</v>
@@ -31545,32 +31841,32 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>10000</v>
+        <v>9096</v>
       </c>
       <c r="K87" t="n">
-        <v>113</v>
+        <v>407</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>151391</v>
+        <v>146745</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.03166036321510102</v>
+        <v>0.05624374689594115</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>136284</v>
+        <v>132992</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -31579,35 +31875,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.02475336862367661</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>10730</v>
+        <v>10000</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>157636</v>
+        <v>151391</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.04125080090626259</v>
+        <v>0.03166036321510102</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>136285</v>
+        <v>136284</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -31616,10 +31912,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>7.337618502538816e-06</v>
+        <v>0.02475336862367661</v>
       </c>
       <c r="J89" t="n">
-        <v>11248</v>
+        <v>10730</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -31628,23 +31924,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>125395</v>
+        <v>157636</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.204528153467482</v>
+        <v>0.04125080090626259</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>110011</v>
+        <v>136285</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -31653,35 +31949,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.1927871739369703</v>
+        <v>7.337618502538816e-06</v>
       </c>
       <c r="J90" t="n">
-        <v>7288</v>
+        <v>11248</v>
       </c>
       <c r="K90" t="n">
-        <v>1173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>134973</v>
+        <v>125395</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.07638263088639898</v>
+        <v>-0.204528153467482</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>132992</v>
+        <v>110011</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -31690,32 +31986,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.2088972920889729</v>
+        <v>-0.1927871739369703</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>7288</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>137128</v>
+        <v>134973</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.0159661561942018</v>
+        <v>0.07638263088639898</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>132992</v>
@@ -31727,32 +32023,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.2088972920889729</v>
       </c>
       <c r="J92" t="n">
-        <v>9097</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>138931</v>
+        <v>137128</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.01314829939910157</v>
+        <v>0.0159661561942018</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>132992</v>
@@ -31767,32 +32063,32 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>9093</v>
+        <v>9097</v>
       </c>
       <c r="K93" t="n">
-        <v>407</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>146745</v>
+        <v>138931</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.05624374689594115</v>
+        <v>0.01314829939910157</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>136122</v>
+        <v>132992</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -31801,35 +32097,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.02353525024061598</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>10071</v>
+        <v>9093</v>
       </c>
       <c r="K94" t="n">
-        <v>94</v>
+        <v>407</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>151391</v>
+        <v>146745</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.03166036321510102</v>
+        <v>0.05624374689594115</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>136285</v>
+        <v>136122</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -31838,71 +32134,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.001197455223990244</v>
+        <v>0.02353525024061598</v>
       </c>
       <c r="J95" t="n">
-        <v>10794</v>
+        <v>10071</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>151391</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.03166036321510102</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>136285</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.001197455223990244</v>
+      </c>
+      <c r="J96" t="n">
+        <v>10794</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>157636</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.04125080090626259</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>7</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>135985</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>365</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.0004769417030487581</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>11280</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>32241</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>25974</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>365</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>3992</v>
       </c>
     </row>
@@ -31918,7 +32251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33968,7 +34301,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -34177,7 +34510,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -34190,7 +34523,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -34208,13 +34541,13 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -34227,7 +34560,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -34251,7 +34584,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -34264,7 +34597,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -34288,7 +34621,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -34301,7 +34634,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34325,7 +34658,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -34338,7 +34671,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -34362,7 +34695,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -34399,7 +34732,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -34412,7 +34745,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -34436,7 +34769,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -34449,7 +34782,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -34473,7 +34806,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -34486,7 +34819,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -34510,7 +34843,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -34523,7 +34856,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -34547,59 +34880,96 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
         <v>7</v>
       </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="4" t="n">
+      <c r="B73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34615,7 +34985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -36739,7 +37109,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -37022,20 +37392,20 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v/>
+        <v>3242</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -37050,10 +37420,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="K65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -37063,7 +37433,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -37096,20 +37466,20 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3240</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -37124,16 +37494,16 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -37146,7 +37516,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -37164,26 +37534,26 @@
         <v>108</v>
       </c>
       <c r="K68" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.0006172839506172839</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -37198,16 +37568,16 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -37217,10 +37587,10 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.0006172839506172839</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -37235,16 +37605,16 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -37257,7 +37627,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -37272,7 +37642,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -37281,17 +37651,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v/>
+        <v>3242</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>5</v>
@@ -37309,20 +37679,20 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="K72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3240</v>
+        <v/>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -37331,7 +37701,7 @@
         <v/>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -37346,16 +37716,16 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -37365,10 +37735,10 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -37386,26 +37756,26 @@
         <v>108</v>
       </c>
       <c r="K74" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.0006172839506172839</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -37420,16 +37790,16 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -37439,34 +37809,34 @@
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0</v>
+        <v>0.0006172839506172839</v>
       </c>
       <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>123</v>
+      </c>
+      <c r="K76" t="n">
         <v>1</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>128</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -37479,46 +37849,83 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>128</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>3242</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
         <v>7</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
         <v>137</v>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B79" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>34</v>
       </c>
     </row>
@@ -37534,7 +37941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -38178,7 +38585,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -38239,7 +38646,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -38252,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -38267,7 +38674,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -38276,7 +38683,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -38289,7 +38696,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -38311,24 +38718,61 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9843</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>634</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="n">
+      <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -38344,7 +38788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -41060,7 +41504,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>26891</v>
@@ -41380,60 +41824,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>33524</v>
+        <v>45739</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2670587463652463</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>5258</v>
+        <v>26891</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.8072651295773615</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1395</v>
+        <v>1904</v>
       </c>
       <c r="K82" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>34324</v>
+        <v>33524</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.02386350077556378</v>
+        <v>-0.2670587463652463</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>3533</v>
+        <v>5258</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -41442,13 +41886,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.3280715100798783</v>
+        <v>-0.8072651295773615</v>
       </c>
       <c r="J83" t="n">
         <v>1395</v>
       </c>
       <c r="K83" t="n">
-        <v>326</v>
+        <v>286</v>
       </c>
     </row>
     <row r="84">
@@ -41464,7 +41908,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.02386350077556378</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -41479,7 +41923,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.3280715100798783</v>
       </c>
       <c r="J84" t="n">
         <v>1395</v>
@@ -41491,23 +41935,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>41503</v>
+        <v>34324</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.2091539447616828</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>8110</v>
+        <v>3533</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -41516,35 +41960,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>1.295499575431645</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1733</v>
+        <v>1395</v>
       </c>
       <c r="K85" t="n">
-        <v>7</v>
+        <v>326</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>42700</v>
+        <v>41503</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.02884128858154832</v>
+        <v>0.2091539447616828</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
-        <v>10929</v>
+        <v>8110</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -41553,32 +41997,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.3475955610357583</v>
+        <v>1.295499575431645</v>
       </c>
       <c r="J86" t="n">
         <v>1733</v>
       </c>
       <c r="K86" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>44397</v>
+        <v>42700</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.0397423887587822</v>
+        <v>0.02884128858154832</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>10929</v>
@@ -41590,35 +42034,35 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>0.3475955610357583</v>
       </c>
       <c r="J87" t="n">
-        <v>1790</v>
+        <v>1733</v>
       </c>
       <c r="K87" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>44576</v>
+        <v>44397</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.004031803950717391</v>
+        <v>0.0397423887587822</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>27039</v>
+        <v>10929</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -41627,35 +42071,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.474059840790557</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1812</v>
+        <v>1790</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>45739</v>
+        <v>44576</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0260902727925341</v>
+        <v>0.004031803950717391</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>27281</v>
+        <v>27039</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -41664,10 +42108,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.008950035134435446</v>
+        <v>1.474059840790557</v>
       </c>
       <c r="J89" t="n">
-        <v>1831</v>
+        <v>1812</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -41676,23 +42120,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>33524</v>
+        <v>45739</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2670587463652463</v>
+        <v>0.0260902727925341</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>5258</v>
+        <v>27281</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -41701,35 +42145,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.8072651295773615</v>
+        <v>0.008950035134435446</v>
       </c>
       <c r="J90" t="n">
-        <v>1395</v>
+        <v>1831</v>
       </c>
       <c r="K90" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>34324</v>
+        <v>33524</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02386350077556378</v>
+        <v>-0.2670587463652463</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>8110</v>
+        <v>5258</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -41738,32 +42182,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.5424115633320654</v>
+        <v>-0.8072651295773615</v>
       </c>
       <c r="J91" t="n">
         <v>1395</v>
       </c>
       <c r="K91" t="n">
-        <v>331</v>
+        <v>286</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>41503</v>
+        <v>34324</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.2091539447616828</v>
+        <v>0.02386350077556378</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>8110</v>
@@ -41775,35 +42219,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.5424115633320654</v>
       </c>
       <c r="J92" t="n">
-        <v>1733</v>
+        <v>1395</v>
       </c>
       <c r="K92" t="n">
-        <v>10</v>
+        <v>331</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>42700</v>
+        <v>41503</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.02884128858154832</v>
+        <v>0.2091539447616828</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
-        <v>10929</v>
+        <v>8110</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -41812,32 +42256,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.3475955610357583</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>1733</v>
       </c>
       <c r="K93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>44397</v>
+        <v>42700</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.0397423887587822</v>
+        <v>0.02884128858154832</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>10929</v>
@@ -41849,35 +42293,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.3475955610357583</v>
       </c>
       <c r="J94" t="n">
-        <v>1790</v>
+        <v>1733</v>
       </c>
       <c r="K94" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>44576</v>
+        <v>44397</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.004031803950717391</v>
+        <v>0.0397423887587822</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>27039</v>
+        <v>10929</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -41886,71 +42330,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>1.474059840790557</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>1812</v>
+        <v>1790</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>44576</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.004031803950717391</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>27039</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>1.474059840790557</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1812</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>45739</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.0260902727925341</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>7</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>26891</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>390</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.008950035134435446</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>1832</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>12215</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>21633</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>390</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>437</v>
       </c>
     </row>
@@ -41966,7 +42447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -44682,7 +45163,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>63879</v>
@@ -45002,60 +45483,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>8512</v>
+        <v>88890</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.9023494860499266</v>
+        <v>0.01975495594713656</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>17587</v>
+        <v>63879</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.7246826030463845</v>
+        <v>0.001236713160819675</v>
       </c>
       <c r="J82" t="n">
-        <v>3856</v>
+        <v>5658</v>
       </c>
       <c r="K82" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>78676</v>
+        <v>8512</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>8.242951127819548</v>
+        <v>-0.9042411969850377</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>43598</v>
+        <v>17587</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -45064,13 +45545,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>1.478990163188719</v>
+        <v>-0.7250226711279277</v>
       </c>
       <c r="J83" t="n">
-        <v>4249</v>
+        <v>3856</v>
       </c>
       <c r="K83" t="n">
-        <v>468</v>
+        <v>770</v>
       </c>
     </row>
     <row r="84">
@@ -45086,7 +45567,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>8.242951127819548</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -45101,7 +45582,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>1.478990163188719</v>
       </c>
       <c r="J84" t="n">
         <v>4249</v>
@@ -45113,23 +45594,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>84794</v>
+        <v>78676</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.07776196044537088</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>51115</v>
+        <v>43598</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -45138,19 +45619,19 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1724161658791688</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>4714</v>
+        <v>4249</v>
       </c>
       <c r="K85" t="n">
-        <v>80</v>
+        <v>468</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -45160,10 +45641,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.07776196044537088</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
         <v>51115</v>
@@ -45175,32 +45656,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.1724161658791688</v>
       </c>
       <c r="J86" t="n">
-        <v>3794</v>
+        <v>4714</v>
       </c>
       <c r="K86" t="n">
-        <v>1183</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>85388</v>
+        <v>84794</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.007005212632969313</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>51115</v>
@@ -45215,32 +45696,32 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>5021</v>
+        <v>3794</v>
       </c>
       <c r="K87" t="n">
-        <v>17</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>86835</v>
+        <v>85388</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.01694617510657235</v>
+        <v>0.007005212632969313</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>63942</v>
+        <v>51115</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -45249,35 +45730,35 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.2509439499168541</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>5301</v>
+        <v>5021</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>87893</v>
+        <v>86835</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01218402717798123</v>
+        <v>0.01694617510657235</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>63879</v>
+        <v>63942</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -45286,10 +45767,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.0009852678990334991</v>
+        <v>0.2509439499168541</v>
       </c>
       <c r="J89" t="n">
-        <v>5519</v>
+        <v>5301</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -45298,23 +45779,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8512</v>
+        <v>87893</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.9031549725234091</v>
+        <v>0.01218402717798123</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>17587</v>
+        <v>63879</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -45323,35 +45804,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.7246826030463845</v>
+        <v>-0.0009852678990334991</v>
       </c>
       <c r="J90" t="n">
-        <v>3856</v>
+        <v>5519</v>
       </c>
       <c r="K90" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>78676</v>
+        <v>8512</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>8.242951127819548</v>
+        <v>-0.9031549725234091</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>43598</v>
+        <v>17587</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -45360,35 +45841,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>1.478990163188719</v>
+        <v>-0.7246826030463845</v>
       </c>
       <c r="J91" t="n">
-        <v>4731</v>
+        <v>3856</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>770</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>84794</v>
+        <v>78676</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.07776196044537088</v>
+        <v>8.242951127819548</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
-        <v>51115</v>
+        <v>43598</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -45397,19 +45878,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.1724161658791688</v>
+        <v>1.478990163188719</v>
       </c>
       <c r="J92" t="n">
-        <v>4714</v>
+        <v>4731</v>
       </c>
       <c r="K92" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -45419,10 +45900,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.07776196044537088</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>51115</v>
@@ -45434,32 +45915,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.1724161658791688</v>
       </c>
       <c r="J93" t="n">
-        <v>3794</v>
+        <v>4714</v>
       </c>
       <c r="K93" t="n">
-        <v>1183</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>85391</v>
+        <v>84794</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.007040592494751987</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>51115</v>
@@ -45474,32 +45955,32 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>5046</v>
+        <v>3794</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>86983</v>
+        <v>85391</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.01864365097024277</v>
+        <v>0.007040592494751987</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>63879</v>
+        <v>51115</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -45508,10 +45989,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.2497114349995109</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>5314</v>
+        <v>5046</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -45520,20 +46001,20 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>88410</v>
+        <v>86983</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.01640550452387248</v>
+        <v>0.01864365097024277</v>
       </c>
       <c r="E96" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>63879</v>
@@ -45542,37 +46023,74 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.2497114349995109</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5314</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>88410</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.01640550452387248</v>
+      </c>
+      <c r="E97" t="n">
+        <v>7</v>
+      </c>
+      <c r="F97" t="n">
+        <v>63879</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>79</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.001236713160819675</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>5557</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>79898</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>46292</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>1701</v>
       </c>
     </row>
@@ -45588,7 +46106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -47712,7 +48230,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -47995,7 +48513,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -48008,7 +48526,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -48023,7 +48541,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -48069,7 +48587,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -48082,7 +48600,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -48100,13 +48618,13 @@
         <v>35</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -48119,7 +48637,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -48143,7 +48661,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -48156,31 +48674,31 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>35</v>
+      </c>
+      <c r="K69" t="n">
         <v>1</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -48193,7 +48711,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -48217,7 +48735,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -48230,7 +48748,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -48254,7 +48772,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -48282,16 +48800,16 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -48304,7 +48822,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -48328,7 +48846,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -48341,7 +48859,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -48365,7 +48883,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -48378,7 +48896,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -48393,16 +48911,16 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -48415,7 +48933,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -48439,59 +48957,96 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
         <v>7</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="n">
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
         <v>-35</v>
       </c>
     </row>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>103148</v>
@@ -11783,7 +11783,7 @@
         <v>0.005177192861888072</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>41946</v>
@@ -15442,7 +15442,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>66160</v>
@@ -18472,7 +18472,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -25013,7 +25013,7 @@
         <v>0.0003818873818401823</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>152356</v>
@@ -28056,7 +28056,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -31641,7 +31641,7 @@
         <v>0.007203422101495265</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>135985</v>
@@ -34523,7 +34523,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -37405,7 +37405,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -38659,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -41837,7 +41837,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>26891</v>
@@ -45496,7 +45496,7 @@
         <v>0.01975495594713656</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>63879</v>
@@ -48526,7 +48526,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>103148</v>
@@ -11783,7 +11783,7 @@
         <v>0.005177192861888072</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>41946</v>
@@ -15442,7 +15442,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>66160</v>
@@ -18472,7 +18472,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -25013,7 +25013,7 @@
         <v>0.0003818873818401823</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>152356</v>
@@ -28056,7 +28056,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -31641,7 +31641,7 @@
         <v>0.007203422101495265</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>135985</v>
@@ -34523,7 +34523,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -37405,7 +37405,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -38659,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -41837,7 +41837,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>26891</v>
@@ -45496,7 +45496,7 @@
         <v>0.01975495594713656</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>63879</v>
@@ -48526,7 +48526,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0.001240676464072077</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>103148</v>
@@ -11783,7 +11783,7 @@
         <v>0.005177192861888072</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>41946</v>
@@ -15442,7 +15442,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>66160</v>
@@ -18472,7 +18472,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -25013,7 +25013,7 @@
         <v>0.0003818873818401823</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>152356</v>
@@ -28056,7 +28056,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -31641,7 +31641,7 @@
         <v>0.007203422101495265</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>135985</v>
@@ -34523,7 +34523,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -37405,7 +37405,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -38659,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -41837,7 +41837,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>26891</v>
@@ -45496,7 +45496,7 @@
         <v>0.01975495594713656</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>63879</v>
@@ -48526,7 +48526,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8139,10 +8139,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>13504</v>
+        <v>13503</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -11801,7 +11801,7 @@
         <v>4533</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -45511,7 +45511,7 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J82" t="n">
-        <v>5658</v>
+        <v>5657</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -11801,7 +11801,7 @@
         <v>4533</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -25031,7 +25031,7 @@
         <v>17229</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8142,7 +8142,7 @@
         <v>13503</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -31659,7 +31659,7 @@
         <v>11681</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -45514,7 +45514,7 @@
         <v>5657</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -28074,7 +28074,7 @@
         <v>203</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -45514,7 +45514,7 @@
         <v>5657</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -31659,7 +31659,7 @@
         <v>11681</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8139,10 +8139,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>13503</v>
+        <v>13502</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -25031,7 +25031,7 @@
         <v>17229</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -31659,7 +31659,7 @@
         <v>11681</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -45514,7 +45514,7 @@
         <v>5657</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -25031,7 +25031,7 @@
         <v>17229</v>
       </c>
       <c r="K82" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
@@ -31659,7 +31659,7 @@
         <v>11681</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -45514,7 +45514,7 @@
         <v>5657</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -25028,10 +25028,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>17229</v>
+        <v>17252</v>
       </c>
       <c r="K82" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -31656,10 +31656,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J82" t="n">
-        <v>11681</v>
+        <v>11694</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -45514,7 +45514,7 @@
         <v>5657</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -25004,13 +25004,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>233142</v>
+        <v>233250</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.0003818873818401823</v>
+        <v>0.0008453012833990551</v>
       </c>
       <c r="E82" t="n">
         <v>3</v>
@@ -25031,7 +25031,7 @@
         <v>17252</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -25047,7 +25047,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.2090142488268952</v>
+        <v>-0.2093804930332261</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>
@@ -31659,7 +31659,7 @@
         <v>11694</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -45487,13 +45487,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>88890</v>
+        <v>88934</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.01975495594713656</v>
+        <v>0.02025972834067548</v>
       </c>
       <c r="E82" t="n">
         <v>3</v>
@@ -45530,7 +45530,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.9042411969850377</v>
+        <v>-0.9042885735489239</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8142,7 +8142,7 @@
         <v>13502</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -11801,7 +11801,7 @@
         <v>4533</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -15460,7 +15460,7 @@
         <v>5175</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -25031,7 +25031,7 @@
         <v>17252</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -41855,7 +41855,7 @@
         <v>1904</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8142,7 +8142,7 @@
         <v>13502</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -11801,7 +11801,7 @@
         <v>4533</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -15460,7 +15460,7 @@
         <v>5175</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -25031,7 +25031,7 @@
         <v>17252</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8139,10 +8139,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>13502</v>
+        <v>13511</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -11798,10 +11798,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J82" t="n">
-        <v>4533</v>
+        <v>4539</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -15457,10 +15457,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J82" t="n">
-        <v>5175</v>
+        <v>5181</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -25028,10 +25028,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>17252</v>
+        <v>17270</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -28071,10 +28071,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -31656,10 +31656,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J82" t="n">
-        <v>11694</v>
+        <v>11700</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -45511,10 +45511,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J82" t="n">
-        <v>5657</v>
+        <v>5663</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8115,13 +8115,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>203367</v>
+        <v>203408</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.001240676464072077</v>
+        <v>0.001442532555448884</v>
       </c>
       <c r="E82" t="n">
         <v>3</v>
@@ -8158,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.05543180555350671</v>
+        <v>-0.05562219775033431</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>
@@ -15460,7 +15460,7 @@
         <v>5181</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -25028,7 +25028,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>17270</v>
+        <v>17277</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -31659,7 +31659,7 @@
         <v>11700</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0.001442532555448884</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>103148</v>
@@ -11783,7 +11783,7 @@
         <v>0.005177192861888072</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>41946</v>
@@ -11801,7 +11801,7 @@
         <v>4539</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -15442,7 +15442,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>66160</v>
@@ -18472,7 +18472,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -25013,7 +25013,7 @@
         <v>0.0008453012833990551</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>152356</v>
@@ -25028,10 +25028,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>17277</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -28056,7 +28056,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -31641,7 +31641,7 @@
         <v>0.007203422101495265</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>135985</v>
@@ -31659,7 +31659,7 @@
         <v>11700</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -34523,7 +34523,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -37405,7 +37405,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -38659,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -41837,7 +41837,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>26891</v>
@@ -45496,7 +45496,7 @@
         <v>0.02025972834067548</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>63879</v>
@@ -45514,7 +45514,7 @@
         <v>5663</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -48526,7 +48526,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8139,7 +8139,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>13511</v>
+        <v>13520</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -11798,10 +11798,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J82" t="n">
-        <v>4539</v>
+        <v>4542</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -15457,10 +15457,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J82" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -25028,10 +25028,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>17295</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -31656,10 +31656,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J82" t="n">
-        <v>11700</v>
+        <v>11707</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -41852,10 +41852,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -45511,10 +45511,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J82" t="n">
-        <v>5663</v>
+        <v>5667</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8139,7 +8139,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>13520</v>
+        <v>13519</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -11798,7 +11798,7 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J82" t="n">
-        <v>4542</v>
+        <v>4544</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -15457,7 +15457,7 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J82" t="n">
-        <v>5182</v>
+        <v>5184</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -25028,7 +25028,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>17295</v>
+        <v>17303</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -41852,7 +41852,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -45511,7 +45511,7 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J82" t="n">
-        <v>5667</v>
+        <v>5671</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8142,7 +8142,7 @@
         <v>13519</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -25031,7 +25031,7 @@
         <v>17303</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -31659,7 +31659,7 @@
         <v>11707</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -45514,7 +45514,7 @@
         <v>5671</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -25031,7 +25031,7 @@
         <v>17303</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01860703311710481</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0.001442532555448884</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>103148</v>
@@ -8139,10 +8139,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>13519</v>
+        <v>13527</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -11783,7 +11783,7 @@
         <v>0.005177192861888072</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>41946</v>
@@ -15442,7 +15442,7 @@
         <v>0.006101308050215082</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>66160</v>
@@ -18472,7 +18472,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -25013,7 +25013,7 @@
         <v>0.0008453012833990551</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>152356</v>
@@ -25028,10 +25028,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>17303</v>
+        <v>17325</v>
       </c>
       <c r="K82" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -28056,7 +28056,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -31641,7 +31641,7 @@
         <v>0.007203422101495265</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>135985</v>
@@ -31656,10 +31656,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J82" t="n">
-        <v>11707</v>
+        <v>11714</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -34523,7 +34523,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -37405,7 +37405,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -38659,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -41837,7 +41837,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>26891</v>
@@ -45496,7 +45496,7 @@
         <v>0.02025972834067548</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>63879</v>
@@ -45511,10 +45511,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J82" t="n">
-        <v>5671</v>
+        <v>5675</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -48526,7 +48526,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -8139,7 +8139,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J82" t="n">
-        <v>13527</v>
+        <v>13528</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -15457,7 +15457,7 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J82" t="n">
-        <v>5184</v>
+        <v>5183</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -25028,7 +25028,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J82" t="n">
-        <v>17325</v>
+        <v>17324</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -45511,7 +45511,7 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J82" t="n">
-        <v>5675</v>
+        <v>5676</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
